--- a/output/roomself_excel/12165.xlsx
+++ b/output/roomself_excel/12165.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>434613</v>
+        <v>128222</v>
       </c>
       <c r="D2" t="n">
-        <v>8244</v>
+        <v>2896</v>
       </c>
       <c r="E2" t="n">
-        <v>1069</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115528</v>
+        <v>100154</v>
       </c>
       <c r="D3" t="n">
-        <v>2744</v>
+        <v>2556</v>
       </c>
       <c r="E3" t="n">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14800</v>
+        <v>115528</v>
       </c>
       <c r="D4" t="n">
-        <v>1096</v>
+        <v>2744</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -532,14 +532,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1176</v>
+        <v>11092</v>
       </c>
       <c r="D5" t="n">
-        <v>280</v>
+        <v>848</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11092</v>
+        <v>41521</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>1948</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -576,20 +576,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41521</v>
+        <v>86048</v>
       </c>
       <c r="D7" t="n">
-        <v>1948</v>
+        <v>2940</v>
       </c>
       <c r="E7" t="n">
-        <v>773</v>
+        <v>288</v>
       </c>
       <c r="F7" t="n">
-        <v>222</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>120189</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2816</v>
+      </c>
+      <c r="E9" t="n">
+        <v>295</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1176</v>
+      </c>
+      <c r="D10" t="n">
+        <v>280</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12165.xlsx
+++ b/output/roomself_excel/12165.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2896</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,12 @@
       <c r="D3" t="n">
         <v>2556</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +547,20 @@
       <c r="D4" t="n">
         <v>2744</v>
       </c>
-      <c r="E4" t="n">
-        <v>298</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +577,12 @@
       <c r="D5" t="n">
         <v>848</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +599,20 @@
       <c r="D6" t="n">
         <v>1948</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +629,27 @@
       <c r="D7" t="n">
         <v>2940</v>
       </c>
-      <c r="E7" t="n">
-        <v>288</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>265</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +667,12 @@
       <c r="D8" t="n">
         <v>1096</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,10 +689,26 @@
       <c r="D9" t="n">
         <v>2816</v>
       </c>
-      <c r="E9" t="n">
-        <v>295</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
+        <v>266</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -651,12 +727,12 @@
       <c r="D10" t="n">
         <v>280</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/12165.xlsx
+++ b/output/roomself_excel/12165.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
